--- a/Result/profitability/6277.xlsx
+++ b/Result/profitability/6277.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.99</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9974999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>58.48249999999999</v>
+        <v>58.81375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.99</v>
       </c>
       <c r="M3" t="n">
-        <v>0.94375</v>
+        <v>0.9437500000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>57.45375</v>
+        <v>57.8325</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.28</v>
       </c>
       <c r="M4" t="n">
-        <v>0.92625</v>
+        <v>0.99</v>
       </c>
       <c r="N4" t="n">
-        <v>56.5525</v>
+        <v>57.00625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -911,7 +911,7 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.31</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8512500000000001</v>
+        <v>0.9625</v>
       </c>
       <c r="N5" t="n">
-        <v>55.695</v>
+        <v>56.06</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.47</v>
       </c>
       <c r="M6" t="n">
-        <v>0.84375</v>
+        <v>0.9149999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>54.85875</v>
+        <v>55.335</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.5</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="N7" t="n">
-        <v>54.23875</v>
+        <v>54.84375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.98</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8250000000000001</v>
+        <v>0.8675</v>
       </c>
       <c r="N8" t="n">
-        <v>53.69875</v>
+        <v>53.97375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6277</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1342</v>
+      </c>
+      <c r="D75" t="n">
+        <v>504</v>
+      </c>
+      <c r="E75" t="n">
+        <v>838</v>
+      </c>
+      <c r="F75" t="n">
+        <v>62.43</v>
+      </c>
+      <c r="G75" t="n">
+        <v>222</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>16.54%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>220</v>
+      </c>
+      <c r="K75" t="n">
+        <v>170</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.98875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>59.54499999999999</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.3399999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3148148148148147</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.200000000000003</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.03652664784990867</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.8899999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.679245283018868</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.920000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.04906738363300289</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
